--- a/data/trans_orig/IP3105-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP3105-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tomar yogures en 2007 (tasa de respuesta: 98,79%)</t>
+          <t>Menores según la frecuencia de tomar yogures o petit suises en 2007 (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3266</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3835</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2077</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9137</t>
+          <t>9658</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14460</t>
+          <t>14982</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9247</t>
+          <t>9078</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19725</t>
+          <t>20342</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10156</t>
+          <t>9812</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20647</t>
+          <t>20620</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6808</t>
+          <t>7612</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17057</t>
+          <t>18465</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19367</t>
+          <t>19404</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34222</t>
+          <t>33906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39766</t>
+          <t>39455</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51287</t>
+          <t>51307</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47535</t>
+          <t>46229</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60202</t>
+          <t>59772</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>91260</t>
+          <t>91475</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>109261</t>
+          <t>109090</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,63%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8402</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>488</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5354</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10123</t>
+          <t>9927</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2493</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10806</t>
+          <t>10386</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,47 +1542,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>5118</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2513</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>9674</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
           <t>0,99%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>5118</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2542</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>10275</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6397</t>
+          <t>6358</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17283</t>
+          <t>17581</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13091</t>
+          <t>12936</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26306</t>
+          <t>25925</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14909</t>
+          <t>15054</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29925</t>
+          <t>29533</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30979</t>
+          <t>31519</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>50673</t>
+          <t>50607</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34595</t>
+          <t>35566</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54316</t>
+          <t>55049</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41013</t>
+          <t>40819</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62033</t>
+          <t>61556</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82238</t>
+          <t>82553</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109466</t>
+          <t>109683</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>166243</t>
+          <t>167637</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>189863</t>
+          <t>190138</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>162850</t>
+          <t>161946</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>186218</t>
+          <t>185809</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>337015</t>
+          <t>336683</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>368974</t>
+          <t>369330</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,23%</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>3290</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>556</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>727</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5858</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>2267</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10399</t>
+          <t>9723</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6761</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17197</t>
+          <t>17470</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10191</t>
+          <t>10379</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>22900</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19751</t>
+          <t>20020</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>35052</t>
+          <t>35437</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21503</t>
+          <t>21384</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35805</t>
+          <t>37392</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21827</t>
+          <t>21413</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37226</t>
+          <t>36800</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47032</t>
+          <t>47709</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>68824</t>
+          <t>69300</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>73993</t>
+          <t>72707</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>90744</t>
+          <t>90761</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>82574</t>
+          <t>80983</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>100414</t>
+          <t>100037</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>161118</t>
+          <t>160722</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>185219</t>
+          <t>185618</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>70,04%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>14049</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>4531</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13917</t>
+          <t>14054</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11289</t>
+          <t>11281</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23684</t>
+          <t>24830</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>6815</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17622</t>
+          <t>18100</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5741</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>15318</t>
+          <t>16031</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>15153</t>
+          <t>15036</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>29150</t>
+          <t>29916</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20112</t>
+          <t>20548</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>34486</t>
+          <t>35909</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21525</t>
+          <t>20789</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>37305</t>
+          <t>37150</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>44695</t>
+          <t>44754</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>68078</t>
+          <t>66697</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34320</t>
+          <t>34615</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>52845</t>
+          <t>53013</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41025</t>
+          <t>40794</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59579</t>
+          <t>60483</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>79361</t>
+          <t>80344</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>106624</t>
+          <t>108260</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,33%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>91233</t>
+          <t>91063</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>113315</t>
+          <t>113409</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>95249</t>
+          <t>94856</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>117196</t>
+          <t>118322</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>194153</t>
+          <t>192026</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>225197</t>
+          <t>225231</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,86%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7641</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19092</t>
+          <t>19385</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7905</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19265</t>
+          <t>18297</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17860</t>
+          <t>17782</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>33237</t>
+          <t>34329</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13793</t>
+          <t>13575</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28424</t>
+          <t>27865</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12567</t>
+          <t>12438</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>25577</t>
+          <t>26035</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>29672</t>
+          <t>29509</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>49553</t>
+          <t>50067</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>50256</t>
+          <t>50336</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>74477</t>
+          <t>74879</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>61339</t>
+          <t>62027</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>87737</t>
+          <t>88943</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>119197</t>
+          <t>118977</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>153924</t>
+          <t>154892</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>116234</t>
+          <t>115779</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>148886</t>
+          <t>149588</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>124782</t>
+          <t>123163</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>157527</t>
+          <t>158510</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>248956</t>
+          <t>250947</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>297311</t>
+          <t>299340</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>389610</t>
+          <t>386466</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>427272</t>
+          <t>428046</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>406411</t>
+          <t>405213</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>447524</t>
+          <t>446018</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>807311</t>
+          <t>804242</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>862470</t>
+          <t>862167</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,93%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tomar yogures en 2012 (tasa de respuesta: 99,07%)</t>
+          <t>Menores según la frecuencia de tomar yogures o petit suises en 2012 (tasa de respuesta: 99,07%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>4749</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>622</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>564</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7194</t>
+          <t>7555</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>485</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5242</t>
+          <t>5424</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8376</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13127</t>
+          <t>13002</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>8988</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7460</t>
+          <t>7917</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18399</t>
+          <t>19708</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74296</t>
+          <t>73675</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84518</t>
+          <t>84621</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73419</t>
+          <t>73647</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82943</t>
+          <t>83370</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>151576</t>
+          <t>149854</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>165362</t>
+          <t>165034</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,23%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>667</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>670</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>5751</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10624</t>
+          <t>10482</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1423</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15948</t>
+          <t>15744</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16379</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>7906</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20424</t>
+          <t>20364</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15704</t>
+          <t>15629</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32104</t>
+          <t>32889</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15257</t>
+          <t>15393</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29572</t>
+          <t>29800</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19772</t>
+          <t>19154</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36354</t>
+          <t>37223</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38100</t>
+          <t>38627</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60578</t>
+          <t>60600</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>185550</t>
+          <t>186577</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>205344</t>
+          <t>204477</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>212578</t>
+          <t>211553</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>232095</t>
+          <t>233076</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>403576</t>
+          <t>405112</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>431546</t>
+          <t>432604</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>86,05%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2569</t>
+          <t>2522</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>10006</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1808</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8227</t>
+          <t>8452</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14879</t>
+          <t>15775</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13776</t>
+          <t>13834</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4621</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14227</t>
+          <t>14938</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11048</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24135</t>
+          <t>24800</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10898</t>
+          <t>10552</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24028</t>
+          <t>23830</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9148</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21316</t>
+          <t>21572</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>22696</t>
+          <t>23053</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39915</t>
+          <t>40803</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15196</t>
+          <t>15111</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30317</t>
+          <t>30518</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15780</t>
+          <t>15733</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29873</t>
+          <t>29209</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33453</t>
+          <t>34490</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>53445</t>
+          <t>54133</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>94617</t>
+          <t>94644</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>114181</t>
+          <t>113999</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>98537</t>
+          <t>98136</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>117539</t>
+          <t>116785</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>197756</t>
+          <t>198794</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>224706</t>
+          <t>226149</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>72,25%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7379</t>
+          <t>7523</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18305</t>
+          <t>19053</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5912</t>
+          <t>6244</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16426</t>
+          <t>16455</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15941</t>
+          <t>15610</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31958</t>
+          <t>30509</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>10909</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23200</t>
+          <t>22618</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8051</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19241</t>
+          <t>18662</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>21334</t>
+          <t>21446</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>38517</t>
+          <t>37711</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>15915</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30055</t>
+          <t>30437</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12455</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25583</t>
+          <t>25668</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>31328</t>
+          <t>31875</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>50907</t>
+          <t>51079</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21481</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37624</t>
+          <t>37600</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22696</t>
+          <t>22797</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38729</t>
+          <t>38857</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>47102</t>
+          <t>48594</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>71426</t>
+          <t>71997</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,79%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>81049</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>101830</t>
+          <t>102257</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>92650</t>
+          <t>93204</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>114280</t>
+          <t>114157</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>179537</t>
+          <t>179374</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>210992</t>
+          <t>209106</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>60,39%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14318</t>
+          <t>14648</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>28805</t>
+          <t>30121</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9693</t>
+          <t>10029</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>22622</t>
+          <t>22858</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27185</t>
+          <t>27558</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>47928</t>
+          <t>47098</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23346</t>
+          <t>22843</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42226</t>
+          <t>40946</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18931</t>
+          <t>19394</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>36345</t>
+          <t>35539</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>45875</t>
+          <t>45814</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>70293</t>
+          <t>70858</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>40568</t>
+          <t>41796</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>63569</t>
+          <t>64038</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>37715</t>
+          <t>37337</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>59836</t>
+          <t>59945</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>83472</t>
+          <t>82683</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>116383</t>
+          <t>115571</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>67887</t>
+          <t>67200</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>95719</t>
+          <t>96611</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>70771</t>
+          <t>70625</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>98061</t>
+          <t>99803</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>145193</t>
+          <t>144665</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>183043</t>
+          <t>183470</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>454107</t>
+          <t>452969</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>490209</t>
+          <t>491484</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>494784</t>
+          <t>495516</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>530838</t>
+          <t>532021</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>958999</t>
+          <t>959177</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1011225</t>
+          <t>1013242</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,45%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tomar yogures en 2016 (tasa de respuesta: 98,69%)</t>
+          <t>Menores según la frecuencia de tomar yogures o petit suises en 2016 (tasa de respuesta: 98,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4773</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>572</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>657</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5926</t>
+          <t>6053</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11110</t>
+          <t>11113</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12534</t>
+          <t>12491</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11136</t>
+          <t>10295</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8768</t>
+          <t>8487</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19667</t>
+          <t>19908</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8886</t>
+          <t>8368</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19411</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25781</t>
+          <t>25541</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24995</t>
+          <t>25256</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41544</t>
+          <t>41495</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,79%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50510</t>
+          <t>50073</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64226</t>
+          <t>63769</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42876</t>
+          <t>42330</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56262</t>
+          <t>55902</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>97243</t>
+          <t>97001</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>116763</t>
+          <t>116638</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,48%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>812</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>6827</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8667</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>829</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5416</t>
+          <t>4889</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8446</t>
+          <t>8124</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>7588</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17922</t>
+          <t>18428</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10606</t>
+          <t>10141</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22916</t>
+          <t>22954</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20252</t>
+          <t>20598</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36594</t>
+          <t>37365</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38599</t>
+          <t>36907</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55851</t>
+          <t>56199</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51697</t>
+          <t>51370</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73795</t>
+          <t>74439</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>94846</t>
+          <t>95739</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>124292</t>
+          <t>125550</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,9%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>135215</t>
+          <t>134126</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>155221</t>
+          <t>156132</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>165311</t>
+          <t>163490</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>189259</t>
+          <t>188801</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>307498</t>
+          <t>304271</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>337422</t>
+          <t>336557</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,1%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>8148</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>2155</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9954</t>
+          <t>10733</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15078</t>
+          <t>15269</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6462</t>
+          <t>6326</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17264</t>
+          <t>16543</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18652</t>
+          <t>19016</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25611</t>
+          <t>24470</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>41983</t>
+          <t>42358</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14586</t>
+          <t>13820</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28454</t>
+          <t>28426</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>44039</t>
+          <t>43789</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>65190</t>
+          <t>65584</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31991</t>
+          <t>32488</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50876</t>
+          <t>51857</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37896</t>
+          <t>37078</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56675</t>
+          <t>57591</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74866</t>
+          <t>74893</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>102052</t>
+          <t>101580</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,22%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>86005</t>
+          <t>85106</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>107493</t>
+          <t>106345</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>103002</t>
+          <t>103526</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>125471</t>
+          <t>125897</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>195122</t>
+          <t>194228</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>226767</t>
+          <t>226898</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,8%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13054</t>
+          <t>11951</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8555</t>
+          <t>8623</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17902</t>
+          <t>17920</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14147</t>
+          <t>14298</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>7112</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18825</t>
+          <t>19896</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14412</t>
+          <t>13621</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>29301</t>
+          <t>28873</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20802</t>
+          <t>20271</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>37774</t>
+          <t>37452</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19188</t>
+          <t>18475</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34760</t>
+          <t>35056</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>43627</t>
+          <t>44097</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>65795</t>
+          <t>66047</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>35675</t>
+          <t>34949</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54603</t>
+          <t>54342</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35607</t>
+          <t>36418</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>55584</t>
+          <t>55927</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>76330</t>
+          <t>75995</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>103103</t>
+          <t>104275</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>72253</t>
+          <t>72862</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>94756</t>
+          <t>94512</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>71804</t>
+          <t>71040</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>94343</t>
+          <t>94079</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>151963</t>
+          <t>151894</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>182263</t>
+          <t>182293</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,7 +10599,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9658</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21862</t>
+          <t>22110</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>6253</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18862</t>
+          <t>18173</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17907</t>
+          <t>18558</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>35827</t>
+          <t>35240</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17914</t>
+          <t>17823</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>34137</t>
+          <t>33928</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11241</t>
+          <t>10675</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>25726</t>
+          <t>24747</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>33360</t>
+          <t>32280</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>54808</t>
+          <t>53422</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>68159</t>
+          <t>68539</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>95967</t>
+          <t>95979</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>56638</t>
+          <t>56555</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>82323</t>
+          <t>82574</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>132399</t>
+          <t>131689</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>170021</t>
+          <t>168947</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>127409</t>
+          <t>128588</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>162621</t>
+          <t>163246</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>155417</t>
+          <t>155840</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>192881</t>
+          <t>194617</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>297408</t>
+          <t>295819</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>346836</t>
+          <t>348267</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>363198</t>
+          <t>363911</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>403231</t>
+          <t>400941</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>402414</t>
+          <t>402076</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>444439</t>
+          <t>443818</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>776806</t>
+          <t>776521</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>835638</t>
+          <t>836099</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,24%</t>
         </is>
       </c>
     </row>
